--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_29-09-2025.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_29-09-2025.xlsx
@@ -576,25 +576,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -639,17 +639,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.99</t>
+          <t>£11.97</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.99</t>
+          <t>£11.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.99</t>
+          <t>£11.97</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -687,25 +687,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -750,12 +750,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£15.30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£15.30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -798,25 +798,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -909,25 +909,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1020,25 +1020,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£21.70</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£21.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£21.70</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1131,25 +1131,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1194,17 +1194,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£21.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£21.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£21.95</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1242,25 +1242,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1305,17 +1305,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1353,25 +1353,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£27.30</t>
+          <t>£27.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£27.30</t>
+          <t>£27.27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£27.30</t>
+          <t>£27.27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1464,25 +1464,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£26.85</t>
+          <t>£26.82</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.85</t>
+          <t>£26.82</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.85</t>
+          <t>£26.82</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1575,25 +1575,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1686,25 +1686,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1749,17 +1749,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£32.95</t>
+          <t>£32.92</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.95</t>
+          <t>£32.92</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£32.95</t>
+          <t>£32.92</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1797,25 +1797,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1860,17 +1860,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£40.20</t>
+          <t>£40.18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£40.20</t>
+          <t>£40.18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£40.20</t>
+          <t>£40.18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1908,25 +1908,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1971,17 +1971,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2019,25 +2019,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2082,17 +2082,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£40.92</t>
+          <t>£40.89</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£40.92</t>
+          <t>£40.89</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£40.92</t>
+          <t>£40.89</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2130,25 +2130,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff7b44b1eb5+80197]
+	GetHandleVerifier [0x0x7ff7b44b1f10+80288]
+	(No symbol) [0x0x7ff7b42302fa]
+	(No symbol) [0x0x7ff7b4287cd7]
+	(No symbol) [0x0x7ff7b4287f9c]
+	(No symbol) [0x0x7ff7b42dba87]
+	(No symbol) [0x0x7ff7b42b03bf]
+	(No symbol) [0x0x7ff7b42d87fb]
+	(No symbol) [0x0x7ff7b42b0153]
+	(No symbol) [0x0x7ff7b4278b02]
+	(No symbol) [0x0x7ff7b42798d3]
+	GetHandleVerifier [0x0x7ff7b476e83d+2949837]
+	GetHandleVerifier [0x0x7ff7b4768c6a+2926330]
+	GetHandleVerifier [0x0x7ff7b47886c7+3055959]
+	GetHandleVerifier [0x0x7ff7b44ccfee+191102]
+	GetHandleVerifier [0x0x7ff7b44d50af+224063]
+	GetHandleVerifier [0x0x7ff7b44baf64+117236]
+	GetHandleVerifier [0x0x7ff7b44bb119+117673]
+	GetHandleVerifier [0x0x7ff7b44a10a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
